--- a/data/trans_orig/P34A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>59027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59382</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>104095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108585</t>
+          <t>106301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157895</t>
+          <t>159030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242698</t>
+          <t>242658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>294230</t>
+          <t>295350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>322872</t>
+          <t>321917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>362900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>576024</t>
+          <t>579038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642843</t>
+          <t>645826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111724</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162391</t>
+          <t>159477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122293</t>
+          <t>121504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154664</t>
+          <t>156342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244906</t>
+          <t>244173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>304370</t>
+          <t>303003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91835</t>
+          <t>92707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131722</t>
+          <t>131302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105669</t>
+          <t>107124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137019</t>
+          <t>136744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208780</t>
+          <t>208395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258528</t>
+          <t>257539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121774</t>
+          <t>125588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85876</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168462</t>
+          <t>170485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212937</t>
+          <t>218186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81964</t>
+          <t>83968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157922</t>
+          <t>150692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271211</t>
+          <t>269725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>468858</t>
+          <t>468478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>884230</t>
+          <t>916053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>446225</t>
+          <t>451617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>502470</t>
+          <t>503980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>959323</t>
+          <t>956208</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1450091</t>
+          <t>1485101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93228</t>
+          <t>88124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231430</t>
+          <t>232375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180907</t>
+          <t>180989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225817</t>
+          <t>225481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261930</t>
+          <t>235857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>437404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74359</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186627</t>
+          <t>183663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147509</t>
+          <t>145805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189272</t>
+          <t>188110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201436</t>
+          <t>198870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355500</t>
+          <t>357779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>121308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69360</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88544</t>
+          <t>93143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>180109</t>
+          <t>181543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62427</t>
+          <t>60464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>81885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164839</t>
+          <t>162388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>255270</t>
+          <t>256325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>317735</t>
+          <t>313946</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>352890</t>
+          <t>348633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>710536</t>
+          <t>695081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>632887</t>
+          <t>630011</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105604</t>
+          <t>1054886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>106622</t>
+          <t>105561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149660</t>
+          <t>147799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92503</t>
+          <t>96059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261855</t>
+          <t>263627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>205556</t>
+          <t>207930</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>387741</t>
+          <t>392300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92614</t>
+          <t>92139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139659</t>
+          <t>137781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88156</t>
+          <t>90004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225293</t>
+          <t>223369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171720</t>
+          <t>184696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>333728</t>
+          <t>332744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149412</t>
+          <t>148144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210370</t>
+          <t>206556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93634</t>
+          <t>95209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139395</t>
+          <t>142040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257296</t>
+          <t>253659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339343</t>
+          <t>333267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76073</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118084</t>
+          <t>118044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>42822</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74284</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123893</t>
+          <t>124843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177261</t>
+          <t>179977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>351471</t>
+          <t>350927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>415512</t>
+          <t>414585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>452488</t>
+          <t>449872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>615502</t>
+          <t>602741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>826109</t>
+          <t>826884</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1012448</t>
+          <t>1011848</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>145897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198762</t>
+          <t>195369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186146</t>
+          <t>192564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>262536</t>
+          <t>264936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357495</t>
+          <t>352879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441539</t>
+          <t>443312</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78931</t>
+          <t>78988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120947</t>
+          <t>120480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>144995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>202461</t>
+          <t>204765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240653</t>
+          <t>242242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307089</t>
+          <t>310709</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>318403</t>
+          <t>310738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>462396</t>
+          <t>457426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>194492</t>
+          <t>193306</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>271469</t>
+          <t>270362</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>551010</t>
+          <t>551412</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>713080</t>
+          <t>712681</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>330344</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>474290</t>
+          <t>473739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>177890</t>
+          <t>171489</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>249846</t>
+          <t>248403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>545513</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>706277</t>
+          <t>700575</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1403834</t>
+          <t>1400195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2001886</t>
+          <t>2024877</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1672264</t>
+          <t>1674126</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2170552</t>
+          <t>2161076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3116160</t>
+          <t>3120845</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3872411</t>
+          <t>3834732</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>471932</t>
+          <t>467717</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>674553</t>
+          <t>670081</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>620377</t>
+          <t>614433</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>843105</t>
+          <t>846267</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1185873</t>
+          <t>1199204</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1485947</t>
+          <t>1484528</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>366725</t>
+          <t>364188</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>520105</t>
+          <t>521798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>514108</t>
+          <t>516866</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>689909</t>
+          <t>689143</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>949168</t>
+          <t>946127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1187350</t>
+          <t>1183007</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>67405</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>51798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>87451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79582</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104095</t>
+          <t>103589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50817</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>70288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>135849</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106301</t>
+          <t>113101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159030</t>
+          <t>164623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>268450</t>
+          <t>293930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242658</t>
+          <t>265291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>295350</t>
+          <t>320819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>342714</t>
+          <t>371111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>321917</t>
+          <t>348001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362900</t>
+          <t>393767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>611164</t>
+          <t>665042</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>579038</t>
+          <t>624905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645826</t>
+          <t>700276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132852</t>
+          <t>143549</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110513</t>
+          <t>119979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159477</t>
+          <t>173077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>138227</t>
+          <t>152022</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121504</t>
+          <t>135367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156342</t>
+          <t>170098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>271078</t>
+          <t>295571</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244173</t>
+          <t>267490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303003</t>
+          <t>330902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>111092</t>
+          <t>125449</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92707</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131302</t>
+          <t>147915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120563</t>
+          <t>130651</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107124</t>
+          <t>114344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136744</t>
+          <t>148866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>231655</t>
+          <t>256100</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208395</t>
+          <t>228882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>257539</t>
+          <t>283000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87461</t>
+          <t>96982</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>76574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125588</t>
+          <t>125856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47545</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135005</t>
+          <t>149709</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>123361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170485</t>
+          <t>179094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>158716</t>
+          <t>172334</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82096</t>
+          <t>144891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218186</t>
+          <t>206095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>223808</t>
+          <t>242380</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150692</t>
+          <t>209923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269725</t>
+          <t>281824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>429608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>468478</t>
+          <t>391329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>916053</t>
+          <t>465854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>476307</t>
+          <t>535871</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>451617</t>
+          <t>508651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>503980</t>
+          <t>566331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1106721</t>
+          <t>965479</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>956208</t>
+          <t>919783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1485101</t>
+          <t>1010879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88124</t>
+          <t>166023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232375</t>
+          <t>220772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>201809</t>
+          <t>229404</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180989</t>
+          <t>205609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225481</t>
+          <t>254415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>376168</t>
+          <t>420311</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235857</t>
+          <t>384301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437404</t>
+          <t>457633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139233</t>
+          <t>156358</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>134013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183663</t>
+          <t>184301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166614</t>
+          <t>181477</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145805</t>
+          <t>159565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188110</t>
+          <t>204206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>305847</t>
+          <t>337835</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198870</t>
+          <t>302734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357779</t>
+          <t>369768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95757</t>
+          <t>99142</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75062</t>
+          <t>77915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121308</t>
+          <t>122550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>45777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70988</t>
+          <t>74118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>145333</t>
+          <t>157441</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>133610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181543</t>
+          <t>187009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83006</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60464</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>118005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>127325</t>
+          <t>138311</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81885</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162388</t>
+          <t>174289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>285157</t>
+          <t>330748</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>256325</t>
+          <t>298340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>313946</t>
+          <t>362260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>489336</t>
+          <t>340075</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348633</t>
+          <t>311653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>695081</t>
+          <t>365457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>774492</t>
+          <t>670824</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>630011</t>
+          <t>631908</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1054886</t>
+          <t>712325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>141326</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>120875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147799</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>181946</t>
+          <t>175252</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96059</t>
+          <t>155378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>263627</t>
+          <t>199270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>307796</t>
+          <t>316578</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>207930</t>
+          <t>288182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>392300</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>113861</t>
+          <t>139910</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>117230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137781</t>
+          <t>166749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>165877</t>
+          <t>188331</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>165428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223369</t>
+          <t>212599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>279738</t>
+          <t>328241</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184696</t>
+          <t>296437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>332744</t>
+          <t>362012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>177381</t>
+          <t>188017</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>160039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206556</t>
+          <t>217803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>119114</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95209</t>
+          <t>107643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142040</t>
+          <t>147796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>296495</t>
+          <t>314768</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253659</t>
+          <t>281757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>333267</t>
+          <t>349306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>103090</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75459</t>
+          <t>82816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118044</t>
+          <t>127888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74288</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>150313</t>
+          <t>164249</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>138135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>179977</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>384138</t>
+          <t>415116</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>350927</t>
+          <t>384146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>414585</t>
+          <t>447132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>501899</t>
+          <t>475117</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>449872</t>
+          <t>444748</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>602741</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>886036</t>
+          <t>890233</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>826884</t>
+          <t>847904</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1011848</t>
+          <t>933215</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>170393</t>
+          <t>174894</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145897</t>
+          <t>151397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>195369</t>
+          <t>201225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>233667</t>
+          <t>252947</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>192564</t>
+          <t>229296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264936</t>
+          <t>277368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>404060</t>
+          <t>427841</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>352879</t>
+          <t>395076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>443312</t>
+          <t>462330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>98462</t>
+          <t>105913</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78988</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120480</t>
+          <t>127413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>178310</t>
+          <t>198746</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144995</t>
+          <t>177513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204765</t>
+          <t>222170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>276771</t>
+          <t>304658</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>242242</t>
+          <t>272616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310709</t>
+          <t>337028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>385967</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>457426</t>
+          <t>476861</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>238907</t>
+          <t>261409</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193306</t>
+          <t>233955</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>270362</t>
+          <t>289961</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>640422</t>
+          <t>689324</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>551412</t>
+          <t>638639</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>712681</t>
+          <t>746470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>447172</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>401215</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>473739</t>
+          <t>498606</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>171489</t>
+          <t>207093</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>248403</t>
+          <t>262965</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>631845</t>
+          <t>680788</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>545513</t>
+          <t>627055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>700575</t>
+          <t>742880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1568158</t>
+          <t>1469402</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1400195</t>
+          <t>1406597</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2024877</t>
+          <t>1531002</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1810256</t>
+          <t>1722176</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1674126</t>
+          <t>1664885</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2161076</t>
+          <t>1772304</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3378413</t>
+          <t>3191578</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3120845</t>
+          <t>3106798</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3834732</t>
+          <t>3273976</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>603454</t>
+          <t>650676</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>467717</t>
+          <t>604745</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>670081</t>
+          <t>705451</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>755648</t>
+          <t>809626</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>614433</t>
+          <t>766475</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>857682</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1359102</t>
+          <t>1460302</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1199204</t>
+          <t>1395217</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1484528</t>
+          <t>1529639</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>527629</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>364188</t>
+          <t>482240</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>521798</t>
+          <t>573044</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>631364</t>
+          <t>699204</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>516866</t>
+          <t>660686</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>689143</t>
+          <t>742218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1094012</t>
+          <t>1226833</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>946127</t>
+          <t>1160389</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1183007</t>
+          <t>1289408</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
